--- a/test-output/data.xlsx
+++ b/test-output/data.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29329"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects_Java\Demo\test-output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBB83F0-6C3A-4BE7-BD89-54A523F9D815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB5D55B-1421-41A0-A808-E3C0623F63A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="5" r:id="rId1"/>
-    <sheet name="Const" sheetId="6" r:id="rId2"/>
+    <sheet name="Accounts" sheetId="7" r:id="rId2"/>
+    <sheet name="Const" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Account_1">Const!$B$1:$C$1</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>First Name</t>
   </si>
@@ -124,6 +125,39 @@
   </si>
   <si>
     <t>automation</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>sandboxqa9@gmail.com</t>
+  </si>
+  <si>
+    <t>https://chatgpt.com/</t>
+  </si>
+  <si>
+    <t>sandboxautomation2@gmail.com</t>
+  </si>
+  <si>
+    <t>c2FuZGJveGF1dG9tYXRpb24yCg==</t>
+  </si>
+  <si>
+    <t>https://app.plus500.com/</t>
+  </si>
+  <si>
+    <t>YXV0b21hdGlvbjExIQ==</t>
+  </si>
+  <si>
+    <t>sandboxqa10@gmail.com</t>
+  </si>
+  <si>
+    <t>cXdlcnR5</t>
   </si>
 </sst>
 </file>
@@ -133,7 +167,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +188,20 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -189,7 +237,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -205,6 +253,15 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -605,6 +662,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0E2DE6B-80FA-49BB-AC12-276B195B8453}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="36.42578125" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="6" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B470DEF3-1360-4827-A4C7-235688089EDF}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
